--- a/photography_forms/005_event_photography_authorization_form--photography_forms.xlsx
+++ b/photography_forms/005_event_photography_authorization_form--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>event_photography_authorization</t>
+          <t>Event Photography Authorization</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>capture_image</t>
+          <t>capture_image_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>capture_image</t>
+          <t>Image Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>share_photos</t>
+          <t>sharing_option</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>share_photos</t>
+          <t>Sharing Option</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>usage</t>
+          <t>storage_option</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>usage</t>
+          <t>Storage Option</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>access_control</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>photographer</t>
+          <t>access_note</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>photographer</t>
+          <t>Access Note</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>photo_release</t>
+          <t>release_policy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>photo_release</t>
+          <t>Release Policy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>photo_credit</t>
+          <t>storage_period</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>photo_credit</t>
+          <t>Storage Period</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>photo_usage</t>
+          <t>access_control_note</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>photo_usage</t>
+          <t>Access Control Note</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,35 +727,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>photo_storage</t>
+          <t>photographer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>photo_storage</t>
+          <t>Photographer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sharing</t>
+          <t>photo_credit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sharing</t>
+          <t>Photo Credit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>storage_note</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>Storage Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>destruction</t>
+          <t>destruction_note</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>destruction</t>
+          <t>Destruction Note</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>access_note</t>
+          <t>release_note</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>access_note</t>
+          <t>Release Note</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>release_note</t>
+          <t>event_photographer_note</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>release_note</t>
+          <t>Event Photographer Note</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,23 +883,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>storage_destruction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>Storage &amp; Destruction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>photographer_note</t>
+          <t>event_photography_authorization_form_note</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>photographer_note</t>
+          <t>Event Photography Authorization Form Note</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>storage_note</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>storage_note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>destruction_note</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>destruction_note</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>access_note</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>access_note</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>photo_credit_note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>photo_credit_note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sharing_note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sharing_note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>storage_note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>storage_note</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>destruction_note</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>destruction_note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +965,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>capture_image_choices</t>
+          <t>capture_image_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>event_details</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Event Details</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>capture_image_choices</t>
+          <t>capture_image_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>candid_moments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Candid Moments</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>share_photos_choices</t>
+          <t>capture_image_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>general_moments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>General Moments</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>share_photos_choices</t>
+          <t>sharing_option_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>share_photos_choices</t>
+          <t>sharing_option_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_sure'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'not_sure'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sharing_choices</t>
+          <t>sharing_option_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'social_media'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'social_media'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sharing_choices</t>
+          <t>access_control_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'email'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sharing_choices</t>
+          <t>access_control_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>access_choices</t>
+          <t>access_control_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'public'}</t>
+          <t>restricted</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'public'}</t>
+          <t>Restricted</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>access_choices</t>
+          <t>release_policy_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'private'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'private'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>access_choices</t>
+          <t>release_policy_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'restricted'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'restricted'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>access_note_choices</t>
+          <t>access_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>access_note_choices</t>
+          <t>access_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>access_note_choices</t>
+          <t>access_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_sure'}</t>
+          <t>restricted</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'not_sure'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>release_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>release_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Restricted</t>
         </is>
       </c>
     </row>
